--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>226.25</v>
+        <v>201.16</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>23.29</v>
+        <v>22.63</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>145.74</v>
+        <v>115.58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,12 +511,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.18 ± 0.12</t>
+          <t>6.24 ± 0.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.35 ± 0.23</t>
+          <t>0.41 ± 0.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.22</v>
+        <v>55.67</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>16.59</v>
+        <v>16.41</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>51.72</v>
+        <v>44.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,12 +556,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.26 ± 0.26</t>
+          <t>0.30 ± 0.30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.17 ± 0.15</t>
+          <t>0.20 ± 0.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -580,33 +580,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83.98</v>
+        <v>66.45</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>73.76000000000001</v>
+        <v>67.92</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>17.08</v>
+        <v>12.72</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.40 ± 0.44</t>
+          <t>1.58 ± 0.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.73 ± 0.37</t>
+          <t>4.66 ± 0.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -625,33 +625,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62.08</v>
+        <v>51.27</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>84.2</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>11.06</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0003***</t>
+          <t>0.0008***</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.34 ± 0.36</t>
+          <t>1.45 ± 0.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.30 ± 0.40</t>
+          <t>4.28 ± 0.42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.48</v>
+        <v>46.55</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>70.38</v>
+        <v>81.5</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>9.48</v>
+        <v>7.43</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0006***</t>
+          <t>0.0028**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.41 ± 0.62</t>
+          <t>0.44 ± 0.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.76 ± 0.31</t>
+          <t>3.34 ± 0.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.85 ± 0.49</t>
+          <t>2.29 ± 0.52</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.1</v>
+        <v>30.79</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>93.52</v>
+        <v>63.79</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>7.71</v>
+        <v>6.27</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0020**</t>
+          <t>0.0060**</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.39 ± 0.20</t>
+          <t>3.15 ± 0.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.16 ± 0.46</t>
+          <t>0.80 ± 0.36</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.29 ± 0.52</t>
+          <t>1.85 ± 0.49</t>
         </is>
       </c>
     </row>
@@ -760,23 +760,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>7.52</v>
+        <v>7.44</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0299*</t>
+          <t>0.0510.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.15 ± 0.07</t>
+          <t>0.18 ± 0.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -805,23 +805,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.49</v>
+        <v>5.31</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>24.85</v>
+        <v>24.65</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0500*</t>
+          <t>0.0793.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.24 ± 0.16</t>
+          <t>0.28 ± 0.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -850,33 +850,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>9.98</v>
+        <v>9.42</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0760.</t>
+          <t>0.1061</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.06 ± 0.06</t>
+          <t>0.07 ± 0.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.44 ± 0.14</t>
+          <t>0.47 ± 0.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.07</v>
+        <v>0.14</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>18.12</v>
+        <v>0.87</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1968</t>
+          <t>0.1375</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.82 ± 0.27</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.33 ± 0.16</t>
+          <t>0.04 ± 0.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.92 ± 0.48</t>
+          <t>0.25 ± 0.25</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>24.06</v>
+        <v>14.09</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.72 ± 0.35</t>
+          <t>0.78 ± 0.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.23 ± 0.19</t>
+          <t>0.26 ± 0.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.92 ± 0.48</t>
         </is>
       </c>
     </row>
@@ -985,33 +985,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>12.01</v>
+        <v>11.67</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.4327</t>
+          <t>0.4317</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.46 ± 0.32</t>
+          <t>0.52 ± 0.36</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.17 ± 0.11</t>
+          <t>0.20 ± 0.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1030,23 +1030,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93</v>
+        <v>11.72</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.5716</t>
+          <t>0.5501</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.24 ± 0.17</t>
+          <t>0.28 ± 0.20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1071,37 +1071,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.93</v>
+        <v>22.97</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.6842</t>
+          <t>0.5768</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.60 ± 0.38</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.11 ± 0.10</t>
+          <t>0.27 ± 0.22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1116,27 +1116,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.39</v>
+        <v>0.12</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>18.94</v>
+        <v>3.88</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.7361</t>
+          <t>0.6678</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.24 ± 0.21</t>
+          <t>0.13 ± 0.11</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.25 ± 0.25</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1229,10 +1229,10 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
